--- a/Mantenimiento/excels/LIMA-LIMA-COMAS.xlsx
+++ b/Mantenimiento/excels/LIMA-LIMA-COMAS.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,11 +484,6 @@
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -536,11 +531,6 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -588,11 +578,6 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -640,11 +625,6 @@
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -692,11 +672,6 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -744,11 +719,6 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -796,11 +766,6 @@
       <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -848,11 +813,6 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -900,11 +860,6 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -952,11 +907,6 @@
       <c r="K10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1004,11 +954,6 @@
       <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1056,11 +1001,6 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1108,11 +1048,6 @@
       <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1160,11 +1095,6 @@
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1212,11 +1142,6 @@
       <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1264,11 +1189,6 @@
       <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1316,11 +1236,6 @@
       <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1368,11 +1283,6 @@
       <c r="K18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1420,11 +1330,6 @@
       <c r="K19" t="n">
         <v>0</v>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1472,11 +1377,6 @@
       <c r="K20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1524,11 +1424,6 @@
       <c r="K21" t="n">
         <v>0</v>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1576,11 +1471,6 @@
       <c r="K22" t="n">
         <v>0</v>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1628,11 +1518,6 @@
       <c r="K23" t="n">
         <v>0</v>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1680,11 +1565,6 @@
       <c r="K24" t="n">
         <v>0</v>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1732,11 +1612,6 @@
       <c r="K25" t="n">
         <v>0</v>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1784,11 +1659,6 @@
       <c r="K26" t="n">
         <v>0</v>
       </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1836,11 +1706,6 @@
       <c r="K27" t="n">
         <v>0</v>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1887,11 +1752,6 @@
       </c>
       <c r="K28" t="n">
         <v>0</v>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/Mantenimiento/excels/LIMA-LIMA-COMAS.xlsx
+++ b/Mantenimiento/excels/LIMA-LIMA-COMAS.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,57 +417,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
@@ -516,20 +504,30 @@
           <t>LA PASCANA</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-11.93643</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-77.04637</v>
-      </c>
-      <c r="I2" t="n">
-        <v>390</v>
-      </c>
-      <c r="J2" t="n">
-        <v>22</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-11.93643</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-77.04637</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -563,20 +561,30 @@
           <t>2033 NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-11.95544</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-77.05324</v>
-      </c>
-      <c r="I3" t="n">
-        <v>604</v>
-      </c>
-      <c r="J3" t="n">
-        <v>25</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-11.95544</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-77.05324</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -610,20 +618,30 @@
           <t>2043 SANGARARA</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-11.91968</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-77.0442</v>
-      </c>
-      <c r="I4" t="n">
-        <v>570</v>
-      </c>
-      <c r="J4" t="n">
-        <v>25</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-11.91968</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-77.0442</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -657,20 +675,30 @@
           <t>2055 PRIMERO DE ABRIL</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-11.91554</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-77.04418</v>
-      </c>
-      <c r="I5" t="n">
-        <v>670</v>
-      </c>
-      <c r="J5" t="n">
-        <v>33</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-11.91554</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-77.04418</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -704,20 +732,30 @@
           <t>2072 LEV SEMIONOVICH VIGOTSKI</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-11.90473</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-77.05477</v>
-      </c>
-      <c r="I6" t="n">
-        <v>354</v>
-      </c>
-      <c r="J6" t="n">
-        <v>15</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-11.90473</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-77.05477</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -751,20 +789,30 @@
           <t>2077 SAN MARTIN DE PORRES DE AÑO NUEVO / SAN MARTIN DE PORRES</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-11.92842</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-77.04119</v>
-      </c>
-      <c r="I7" t="n">
-        <v>942</v>
-      </c>
-      <c r="J7" t="n">
-        <v>42</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-11.92842</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-77.04119</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -798,20 +846,30 @@
           <t>3060 ALFONSO UGARTE VERNAL</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-11.93905</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-77.05315</v>
-      </c>
-      <c r="I8" t="n">
-        <v>557</v>
-      </c>
-      <c r="J8" t="n">
-        <v>23</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-11.93905</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-77.05315</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>557</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -845,20 +903,30 @@
           <t>8160 LOS CHASQUIS</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-11.93434</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-77.06113999999999</v>
-      </c>
-      <c r="I9" t="n">
-        <v>907</v>
-      </c>
-      <c r="J9" t="n">
-        <v>39</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-11.93434</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-77.06114</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -892,20 +960,30 @@
           <t>3085 PEDRO VILCA APAZA</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-11.95164</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-77.05717</v>
-      </c>
-      <c r="I10" t="n">
-        <v>389</v>
-      </c>
-      <c r="J10" t="n">
-        <v>15</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-11.95164</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-77.05717</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>389</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -939,20 +1017,30 @@
           <t>8156 PERUANO ALEMAN</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-11.90871</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-77.04277999999999</v>
-      </c>
-      <c r="I11" t="n">
-        <v>309</v>
-      </c>
-      <c r="J11" t="n">
-        <v>14</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-11.90871</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-77.04278</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -986,20 +1074,30 @@
           <t>8157 REPUBLICA DE FRANCIA</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-11.91219</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-77.04131</v>
-      </c>
-      <c r="I12" t="n">
-        <v>522</v>
-      </c>
-      <c r="J12" t="n">
-        <v>21</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-11.91219</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-77.04131</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1033,20 +1131,30 @@
           <t>8173 SANTA ISOLINA</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-11.95911</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-77.06225999999999</v>
-      </c>
-      <c r="I13" t="n">
-        <v>446</v>
-      </c>
-      <c r="J13" t="n">
-        <v>19</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-11.95911</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-77.06226</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>446</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1080,20 +1188,30 @@
           <t>2022 SINCHI ROCA</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-11.93045</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-77.04964</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1787</v>
-      </c>
-      <c r="J14" t="n">
-        <v>84</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-11.93045</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-77.04964</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1787</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1127,20 +1245,30 @@
           <t>ESTADOS UNIDOS</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-11.965191</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-77.05676</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1751</v>
-      </c>
-      <c r="J15" t="n">
-        <v>91</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-11.965191</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-77.05676</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1751</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1174,20 +1302,30 @@
           <t>2026 SIMON BOLIVAR</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-11.95063</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-77.06313</v>
-      </c>
-      <c r="I16" t="n">
-        <v>942</v>
-      </c>
-      <c r="J16" t="n">
-        <v>50</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-11.95063</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-77.06313</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1221,20 +1359,30 @@
           <t>2085 SAN AGUSTIN</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-11.9323</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-77.05056</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1844</v>
-      </c>
-      <c r="J17" t="n">
-        <v>79</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-11.9323</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-77.05056</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1844</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1268,20 +1416,30 @@
           <t>3096 FRANZ TAMAYO SOLARES</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-11.92383</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-77.05296</v>
-      </c>
-      <c r="I18" t="n">
-        <v>926</v>
-      </c>
-      <c r="J18" t="n">
-        <v>41</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-11.92383</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-77.05296</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>926</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1315,20 +1473,30 @@
           <t>2038 INCA GARCILASO DE LA VEGA</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-11.917908</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-77.029028</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1135</v>
-      </c>
-      <c r="J19" t="n">
-        <v>33</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-11.917908</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-77.029028</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1135</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1362,20 +1530,30 @@
           <t>JOSE MARTI</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-11.95403</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-77.05587</v>
-      </c>
-      <c r="I20" t="n">
-        <v>711</v>
-      </c>
-      <c r="J20" t="n">
-        <v>32</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-11.95403</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-77.05587</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>711</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1409,20 +1587,30 @@
           <t>EL AMAUTA</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-11.92998</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-77.06647</v>
-      </c>
-      <c r="I21" t="n">
-        <v>835</v>
-      </c>
-      <c r="J21" t="n">
-        <v>37</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-11.92998</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-77.06647</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>835</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -1456,20 +1644,30 @@
           <t>JUAN PABLO VIZCARDO Y GUZMAN</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-11.92554</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-77.04526</v>
-      </c>
-      <c r="I22" t="n">
-        <v>354</v>
-      </c>
-      <c r="J22" t="n">
-        <v>26</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-11.92554</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-77.04526</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1503,20 +1701,30 @@
           <t>MARISCAL ANDRES AVELINO CACERES DORREGARAY</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-11.91639</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-77.03376</v>
-      </c>
-      <c r="I23" t="n">
-        <v>700</v>
-      </c>
-      <c r="J23" t="n">
-        <v>60</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-11.91639</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-77.03376</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -1550,20 +1758,30 @@
           <t>LA ALBORADA FRANCESA</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-11.9123</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-77.04734000000001</v>
-      </c>
-      <c r="I24" t="n">
-        <v>673</v>
-      </c>
-      <c r="J24" t="n">
-        <v>37</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-11.9123</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-77.04734</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -1597,20 +1815,30 @@
           <t>PERUANO SUIZO</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-11.96703</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-77.06010999999999</v>
-      </c>
-      <c r="I25" t="n">
-        <v>785</v>
-      </c>
-      <c r="J25" t="n">
-        <v>38</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-11.96703</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-77.06011</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>785</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -1644,20 +1872,30 @@
           <t>SAN CARLOS</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-11.90316</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-77.04262</v>
-      </c>
-      <c r="I26" t="n">
-        <v>375</v>
-      </c>
-      <c r="J26" t="n">
-        <v>19</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-11.90316</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-77.04262</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -1691,20 +1929,30 @@
           <t>SAN FELIPE</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-11.89896</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-77.04062999999999</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1427</v>
-      </c>
-      <c r="J27" t="n">
-        <v>65</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-11.89896</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-77.04063</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1427</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -1738,20 +1986,30 @@
           <t>8181 HEROES DEL ALTO CENEPA</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-11.92344</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-77.06047</v>
-      </c>
-      <c r="I28" t="n">
-        <v>744</v>
-      </c>
-      <c r="J28" t="n">
-        <v>34</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-11.92344</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-77.06047</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>
